--- a/EIB/Submit_Job_Profile_v46.0.xlsx
+++ b/EIB/Submit_Job_Profile_v46.0.xlsx
@@ -305,38 +305,6 @@
     <author>None</author>
   </authors>
   <commentList>
-    <comment ref="C6" authorId="0" shapeId="0">
-      <text>
-        <t>Auto Complete_x000D_
-_x000D_
-When set to "true" or "1", the business process is automatically processed. This means that all approvals will be automatically approved in the system, all reviews and to-do's will be automatically by-passed, and all notifications will be automatically suppressed._x000D_
-_x000D_
-Run Now_x000D_
-_x000D_
-Indicates the transaction should process to completion before the response is generated.  
-Note: All &lt; v12 operations will process with Run_Now = True for backwards compatibility but please review this setting in your environment for performance conditions.</t>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
-        <t>Enforces all critical validation conditions defined on the initiation step. When any critical validation condition is true, the validation error blocks the step from exiting and we won't create a business process event. Note: To handle exceptions on Import web services, set the ‘x-handle-import-process-errors’ header to 1.</t>
-      </text>
-    </comment>
-    <comment ref="E6" authorId="0" shapeId="0">
-      <text>
-        <t>Free form comment regarding the business process.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>None</author>
-  </authors>
-  <commentList>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>Contains the job profile data.</t>
@@ -1865,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E7"/>
+  <dimension ref="B2:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" style="13" min="1" max="1"/>
@@ -1888,36 +1856,116 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Business Process</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Processing Instruction</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Discard on Exit Validation Error</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Processing Comment</t>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Systems_Engineer</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Do you enjoy working with clients? Join our Academy program - intensive training designed to teach smart young professionals to become world-class consultants. Work and learn from experienced Consultants and team members while contributing to developing solutions for customer's business issues.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Submit Job Profile</t>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HR_Consultant</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ILP HR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Manage a team that provides excellence in customer care; research and resolve telephone and written inquiries. Answer a variety of questions regarding the firm's products and services. Lead the team in achieving regional and divisional goals in quality through individual and collaborative efforts. Ability to work in both a structured and unstructured and fast paced environment with rigorous performance metrics. Must have the ability to multi-task, prioritize and organize work and inspire others.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>General_Manager</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Provides the  for planning and directing the operations of an organization to ensure and enhance performance, productivity and profitability.</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1982,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
